--- a/tests/fixtures/15_anual_budget/pattern.xlsx
+++ b/tests/fixtures/15_anual_budget/pattern.xlsx
@@ -1565,7 +1565,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:C5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:C6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:C8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:C10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cell:1</t>
+          <t>cell:B12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
